--- a/artifacts/exports/shuori-demo-readiness.xlsx
+++ b/artifacts/exports/shuori-demo-readiness.xlsx
@@ -29,7 +29,7 @@
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 10:10:35 JST · Asia/Tokyo · demo · version 1.2.0</t>
+    <t>Generated 2026-10-08 17:07:04 JST · Asia/Tokyo · demo · version 1.3.0</t>
   </si>
   <si>
     <t>readiness | All records in the stated scope | Date: 2026-10-08 | View label: Administrative readiness as of 2026-10-08</t>

--- a/artifacts/exports/shuori-demo-readiness.xlsx
+++ b/artifacts/exports/shuori-demo-readiness.xlsx
@@ -29,7 +29,7 @@
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 17:07:04 JST · Asia/Tokyo · demo · version 1.3.0</t>
+    <t>Generated 2026-10-08 17:31:53 JST · Asia/Tokyo · demo · version 1.3.0</t>
   </si>
   <si>
     <t>readiness | All records in the stated scope | Date: 2026-10-08 | View label: Administrative readiness as of 2026-10-08</t>

--- a/artifacts/exports/shuori-demo-readiness.xlsx
+++ b/artifacts/exports/shuori-demo-readiness.xlsx
@@ -29,7 +29,7 @@
     <t>守織 SHUORI · Workbook overview</t>
   </si>
   <si>
-    <t>Generated 2026-10-08 17:31:53 JST · Asia/Tokyo · demo · version 1.3.0</t>
+    <t>Generated 2026-10-08 18:03:46 JST · Asia/Tokyo · demo · version 1.4.0</t>
   </si>
   <si>
     <t>readiness | All records in the stated scope | Date: 2026-10-08 | View label: Administrative readiness as of 2026-10-08</t>
